--- a/DATA/data source.xlsx
+++ b/DATA/data source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\knockoff\Asubmit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aresearch\knockoff\Asubmit\DATA and RESULTS\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{384DEF15-A00D-4DF1-95A2-68147867B4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A6E4F54-38CD-465B-A798-EF82D8A1145D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2880" yWindow="1300" windowWidth="16270" windowHeight="9540" xr2:uid="{77DCC81C-0672-4DBF-ABE7-DD9F2096B317}"/>
+    <workbookView xWindow="3830" yWindow="3640" windowWidth="18060" windowHeight="10040" xr2:uid="{77DCC81C-0672-4DBF-ABE7-DD9F2096B317}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>simulated data</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -88,6 +88,20 @@
   <si>
     <t>https://doi.org/10.1016/j.cell.2009.01.055</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>source</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://doi.org/10.1186/s40168-020-00995-7</t>
+  </si>
+  <si>
+    <t>human skin microbiota</t>
   </si>
 </sst>
 </file>
@@ -467,13 +481,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{704107C9-916B-433A-9A3D-616C44BED14F}">
-  <dimension ref="A2:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.4140625" customWidth="1"/>
-    <col min="2" max="2" width="33.1640625" customWidth="1"/>
+    <col min="2" max="2" width="33.08203125" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+    </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
@@ -544,6 +566,14 @@
       </c>
       <c r="B10" s="1" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
